--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12T22:27:02Z</t>
+          <t>2026-09-13T22:31:32Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-09-12T22:27:02Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-09-13T22:31:32Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13T22:31:32Z</t>
+          <t>2026-09-14T23:16:43Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-09-13T22:31:32Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-09-14T23:16:43Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:16:43Z</t>
+          <t>2026-09-15T23:01:39Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-09-14T23:16:43Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-09-15T23:01:39Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15T23:01:39Z</t>
+          <t>2026-09-16T23:07:48Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-09-15T23:01:39Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-09-16T23:07:48Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T23:07:48Z</t>
+          <t>2026-09-17T17:37:55Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-09-16T23:07:48Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-09-17T17:37:55Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T17:37:55Z</t>
+          <t>2026-09-17T22:58:10Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-09-17T17:37:55Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-09-17T22:58:10Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T22:58:10Z</t>
+          <t>2026-09-18T22:43:53Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-09-17T22:58:10Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-09-18T22:43:53Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18T22:43:53Z</t>
+          <t>2026-09-19T22:23:12Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-09-18T22:43:53Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-09-19T22:23:12Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19T22:23:12Z</t>
+          <t>2026-09-20T22:35:41Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-09-19T22:23:12Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-09-20T22:35:41Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20T22:35:41Z</t>
+          <t>2026-09-21T23:27:49Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-09-20T22:35:41Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-09-21T23:27:49Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:27:49Z</t>
+          <t>2026-09-22T17:38:14Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-09-21T23:27:49Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-09-22T17:38:14Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T17:38:14Z</t>
+          <t>2026-09-22T23:08:03Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-09-22T17:38:14Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-09-22T23:08:03Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T23:08:03Z</t>
+          <t>2026-09-23T23:02:38Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-09-22T23:08:03Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-09-23T23:02:38Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23T23:02:38Z</t>
+          <t>2026-09-24T23:17:58Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-09-23T23:02:38Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-09-24T23:17:58Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24T23:17:58Z</t>
+          <t>2026-09-25T23:23:39Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-09-24T23:17:58Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-09-25T23:23:39Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25T23:23:39Z</t>
+          <t>2026-09-26T23:03:46Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-09-25T23:23:39Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-09-26T23:03:46Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26T23:03:46Z</t>
+          <t>2026-09-27T23:13:02Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-09-26T23:03:46Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-09-27T23:13:02Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27T23:13:02Z</t>
+          <t>2026-09-29T00:28:22Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-09-27T23:13:02Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-09-29T00:28:22Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:28:22Z</t>
+          <t>2026-09-29T23:51:57Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-09-29T00:28:22Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-09-29T23:51:57Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29T23:51:57Z</t>
+          <t>2026-10-01T00:02:20Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-09-29T23:51:57Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-10-01T00:02:20Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:20Z</t>
+          <t>2026-10-02T00:01:23Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-10-01T00:02:20Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-10-02T00:01:23Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T00:01:23Z</t>
+          <t>2026-10-02T18:24:24Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-10-02T00:01:23Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-10-02T18:24:24Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T18:24:24Z</t>
+          <t>2026-10-02T23:55:31Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-10-02T18:24:24Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-10-02T23:55:31Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02T23:55:31Z</t>
+          <t>2026-10-03T23:14:13Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-10-02T23:55:31Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-10-03T23:14:13Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03T23:14:13Z</t>
+          <t>2026-10-04T23:25:19Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-10-03T23:14:13Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-10-04T23:25:19Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:25:19Z</t>
+          <t>2026-10-06T01:22:21Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-10-04T23:25:19Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-10-06T01:22:21Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T01:22:21Z</t>
+          <t>2026-10-06T23:57:00Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-10-06T01:22:21Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-10-06T23:57:00Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T23:57:00Z</t>
+          <t>2026-10-07T19:19:48Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-10-06T23:57:00Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-10-07T19:19:48Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T19:19:48Z</t>
+          <t>2026-10-08T00:18:15Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-10-07T19:19:48Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-10-08T00:18:15Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T00:18:15Z</t>
+          <t>2026-10-09T00:32:03Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-10-08T00:18:15Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-10-09T00:32:03Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T00:32:03Z</t>
+          <t>2026-10-10T00:11:25Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-10-09T00:32:03Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-10-10T00:11:25Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T00:11:25Z</t>
+          <t>2026-10-10T23:42:25Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-10-10T00:11:25Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-10-10T23:42:25Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10T23:42:25Z</t>
+          <t>2026-10-11T23:49:14Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-10-10T23:42:25Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-10-11T23:49:14Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11T23:49:14Z</t>
+          <t>2026-10-12T21:43:48Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-10-11T23:49:14Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-10-12T21:43:48Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12T21:43:48Z</t>
+          <t>2026-10-13T02:10:28Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-10-12T21:43:48Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-10-13T02:10:28Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T02:10:28Z</t>
+          <t>2026-10-13T23:48:08Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-10-13T02:10:28Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-10-13T23:48:08Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13T23:48:08Z</t>
+          <t>2026-10-14T23:20:56Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-10-13T23:48:08Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-10-14T23:20:56Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T23:20:56Z</t>
+          <t>2026-10-15T23:09:49Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-10-14T23:20:56Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-10-15T23:09:49Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15T23:09:49Z</t>
+          <t>2026-10-16T22:56:27Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-10-15T23:09:49Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-10-16T22:56:27Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16T22:56:27Z</t>
+          <t>2026-10-17T16:23:41Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-10-16T22:56:27Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-10-17T16:23:41Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:41Z</t>
+          <t>2026-10-17T22:30:21Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-10-17T16:23:41Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-10-17T22:30:21Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17T22:30:21Z</t>
+          <t>2026-10-18T22:31:22Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-10-17T22:30:21Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-10-18T22:31:22Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18T22:31:22Z</t>
+          <t>2026-10-19T23:50:40Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-10-18T22:31:22Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-10-19T23:50:40Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:50:40Z</t>
+          <t>2026-10-20T23:17:02Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-10-19T23:50:40Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-10-20T23:17:02Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:17:02Z</t>
+          <t>2026-10-21T23:30:21Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-10-20T23:17:02Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-10-21T23:30:21Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21T23:30:21Z</t>
+          <t>2026-10-22T17:58:31Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-10-21T23:30:21Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-10-22T17:58:31Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T17:58:31Z</t>
+          <t>2026-10-22T23:29:29Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-10-22T17:58:31Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-10-22T23:29:29Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T23:29:29Z</t>
+          <t>2026-10-23T23:18:17Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-10-22T23:29:29Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-10-23T23:18:17Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:18:17Z</t>
+          <t>2026-10-24T22:37:22Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-10-23T23:18:17Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-10-24T22:37:22Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T22:37:22Z</t>
+          <t>2026-10-25T22:44:00Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-10-24T22:37:22Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-10-25T22:44:00Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T22:44:00Z</t>
+          <t>2026-10-26T23:58:54Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-10-25T22:44:00Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-10-26T23:58:54Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T23:58:54Z</t>
+          <t>2026-10-27T23:53:49Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-10-26T23:58:54Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-10-27T23:53:49Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:53:49Z</t>
+          <t>2026-10-29T00:09:57Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-10-27T23:53:49Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-10-29T00:09:57Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T00:09:57Z</t>
+          <t>2026-10-30T00:03:41Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-10-29T00:09:57Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-10-30T00:03:41Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_historico_anual.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:03:41Z</t>
+          <t>2026-10-30T23:56:22Z</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-10-30T00:03:41Z"}</t>
+          <t>{"dataset_id": "bcv_pib_historico_anual", "title": "Producto interno bruto histórico anual", "table": "PIB histórico anual", "source_file": "7_1_14_anual.xls", "base": "1957/1968/1984/1997", "price_type": "Precios constantes", "measure": "Nivel", "frequency": "Anual", "period": "2017", "year": 2017, "quarter": null, "classification": "Total economía", "component": "Producto interno bruto", "value": 392393.12, "unit": "Millones de bolívares a precios constantes", "status": "", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/7_1_14_anual.xls", "fetched_at": "2026-10-30T23:56:22Z"}</t>
         </is>
       </c>
     </row>
